--- a/Portabox-SEO-Build-Sheet.xlsx
+++ b/Portabox-SEO-Build-Sheet.xlsx
@@ -5,6 +5,7 @@
   <sheets>
     <sheet state="visible" name="Read me first" sheetId="1" r:id="rId5"/>
     <sheet state="visible" name="Build sheet" sheetId="2" r:id="rId6"/>
+    <sheet name="Live links" sheetId="3" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">'Build sheet'!$A$1:$M$127</definedName>
@@ -8114,4 +8115,4970 @@
   <pageSetup orientation="landscape"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="5"/>
+    <col min="2" max="2" width="24"/>
+    <col min="3" max="3" width="18"/>
+    <col min="4" max="4" width="40"/>
+    <col min="5" max="5" width="64"/>
+    <col min="6" max="6" width="14"/>
+    <col min="7" max="7" width="30"/>
+    <col min="8" max="8" width="34"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Page type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Path</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Full link</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Target keyword</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Old URL to 301</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1. Quick wins, no build</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Google Business Profile</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>GBP: Brisbane depot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Not a page</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>storage near me</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1. Quick wins, no build</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Google Business Profile</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>GBP: Sydney depot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Not a page</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>storage near me</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1. Quick wins, no build</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Google Business Profile</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>GBP: Melbourne depot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Not a page</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>storage near me</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1. Quick wins, no build</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Google Business Profile</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>GBP: Adelaide depot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Not a page</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>storage near me</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1. Quick wins, no build</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Title fix</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>/self-storage/brisbane/</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/brisbane/</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>self storage brisbane</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Storage &amp; Moving Containers in South East Queensland</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1. Quick wins, no build</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Title fix</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>/self-storage/sydney/</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/sydney/</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>self storage sydney</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Storage &amp; Moving Containers in Greater Sydney</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1. Quick wins, no build</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Title fix</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>/self-storage/melbourne/</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/melbourne/</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>self storage melbourne</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Storage &amp; Moving Containers in Victoria</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1. Quick wins, no build</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Title fix</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>/self-storage/adelaide/</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/adelaide/</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>self storage adelaide</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Storage &amp; Moving Containers in South Australia</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1. Quick wins, no build</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Technical</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>robots.txt</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/robots.txt</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1. Quick wins, no build</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Technical</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>sitemap.xml</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/sitemap.xml</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1. Quick wins, no build</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Technical</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>JSON-LD schema layer</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Not a page</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2. Region hubs</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Region hub</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>/self-storage/brisbane/</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/brisbane/</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>storage brisbane</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>/locations/brisbane/ (301 to here)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2. Region hubs</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Region hub</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>/self-storage/sydney/</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/sydney/</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>self storage sydney</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>/locations/sydney/ (301 to here)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2. Region hubs</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Region hub</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>/self-storage/melbourne/</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/melbourne/</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>self storage melbourne</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>/locations/melbourne/ (301 to here)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2. Region hubs</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Region hub</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>/self-storage/adelaide/</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/adelaide/</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>self storage adelaide</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>/locations/adelaide/ (301 to here)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2. Region hubs</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Region hub</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>/self-storage/gold-coast/</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/gold-coast/</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>self storage gold coast</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>/locations/gold-coast/ (301 to here)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2. Region hubs</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Region hub</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>/self-storage/central-coast/</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/central-coast/</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>self storage central coast</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>/locations/central-coast/ (301 to here)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2. Region hubs</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Region hub</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>/self-storage/newcastle/</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/newcastle/</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>self storage newcastle</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2. Region hubs</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Region hub</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>/self-storage/wollongong/</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/wollongong/</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>self storage wollongong</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>3. Rescue: top 10</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Suburb page</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>/self-storage/central-coast/west-gosford/</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/central-coast/west-gosford/</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>storage west gosford</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>/locations/west-gosford/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>3. Rescue: top 10</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Suburb page</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>/self-storage/melbourne/hoppers-crossing/</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/melbourne/hoppers-crossing/</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>storage hoppers crossing</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>/locations/hoppers-crossing/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>3. Rescue: top 10</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Suburb page</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>/self-storage/melbourne/box-hill/</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/melbourne/box-hill/</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>storage box hill</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>/locations/box-hill/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>3. Rescue: top 10</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Suburb page</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>/self-storage/adelaide/port-adelaide/</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/adelaide/port-adelaide/</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>storage port adelaide</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>/locations/port-adelaide/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>3. Rescue: top 10</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Suburb page</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>/self-storage/brisbane/ipswich/</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/brisbane/ipswich/</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>storage ipswich</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>/locations/ipswich/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>3. Rescue: top 10</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Suburb page</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>/self-storage/sydney/blacktown/</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/sydney/blacktown/</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>storage blacktown</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>/locations/blacktown/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>3. Rescue: top 10</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Suburb page</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>/self-storage/gold-coast/tweed-heads/</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/gold-coast/tweed-heads/</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>storage tweed heads</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>/locations/tweed-heads/</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>3. Rescue: top 10</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Suburb page</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>/self-storage/sydney/castle-hill/</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/sydney/castle-hill/</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>storage castle hill</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>/locations/castle-hill/</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>3. Rescue: top 10</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Suburb page</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>/self-storage/brisbane/browns-plains/</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/brisbane/browns-plains/</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>storage browns plains</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>/locations/browns-plains/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>3. Rescue: top 10</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Suburb page</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>/self-storage/melbourne/pakenham/</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/melbourne/pakenham/</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>storage pakenham</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>/locations/pakenham/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>4. Rescue: next 16</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Suburb page</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>/self-storage/central-coast/rutherford/</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/central-coast/rutherford/</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>storage rutherford</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>/locations/rutherford/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>4. Rescue: next 16</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Suburb page</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>/self-storage/sydney/artarmon/</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/sydney/artarmon/</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>storage artarmon</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>/locations/artarmon/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>4. Rescue: next 16</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Suburb page</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>/self-storage/gold-coast/robina/</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/gold-coast/robina/</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>storage robina</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>/locations/robina/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>4. Rescue: next 16</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Suburb page</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>/self-storage/CHECK/richmond/</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/CHECK/richmond/</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>storage richmond</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>/locations/richmond/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>4. Rescue: next 16</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Suburb page</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>/self-storage/CHECK/queanbeyan/</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/CHECK/queanbeyan/</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>storage queanbeyan</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>/locations/queanbeyan/</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>4. Rescue: next 16</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Suburb page</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>/self-storage/sydney/alexandria/</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/sydney/alexandria/</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>storage alexandria</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>/locations/alexandria/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>4. Rescue: next 16</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Suburb page</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>/self-storage/sydney/dee-why/</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/sydney/dee-why/</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>storage dee why</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>/locations/dee-why/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>4. Rescue: next 16</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Suburb page</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>/self-storage/melbourne/cheltenham/</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/melbourne/cheltenham/</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>storage cheltenham</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>/locations/cheltenham/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>4. Rescue: next 16</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Suburb page</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>/self-storage/melbourne/carrum-downs/</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/melbourne/carrum-downs/</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>storage carrum downs</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>/locations/carrum-downs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>4. Rescue: next 16</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Suburb page</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>/self-storage/gold-coast/currumbin/</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/gold-coast/currumbin/</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>storage currumbin</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>/locations/currumbin/</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>4. Rescue: next 16</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Suburb page</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>/self-storage/sydney/hornsby/</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/sydney/hornsby/</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>storage hornsby</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>/locations/hornsby/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>4. Rescue: next 16</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Suburb page</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>/self-storage/CHECK/springwood/</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/CHECK/springwood/</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>storage springwood</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>/locations/springwood/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>4. Rescue: next 16</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Suburb page</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>/self-storage/sydney/chatswood/</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/sydney/chatswood/</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>storage chatswood</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>/locations/chatswood/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>4. Rescue: next 16</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Suburb page</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>/self-storage/brisbane/logan/</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/brisbane/logan/</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>storage logan</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>/locations/logan/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>4. Rescue: next 16</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Suburb page</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>/self-storage/CHECK/mitchell/</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/CHECK/mitchell/</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>storage mitchell</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>/locations/mitchell/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>4. Rescue: next 16</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Suburb page</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>/self-storage/gold-coast/nerang/</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/gold-coast/nerang/</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>storage nerang</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>/locations/nerang/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>5. Rescue: remainder</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Suburb page</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>/self-storage/gold-coast/hope-island/</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/gold-coast/hope-island/</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>storage hope island</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>/locations/hope-island/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>5. Rescue: remainder</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Suburb page</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>/self-storage/sydney/bondi-junction/</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/sydney/bondi-junction/</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>storage bondi junction</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>/locations/bondi-junction/</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>5. Rescue: remainder</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Suburb page</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>/self-storage/brisbane/milton/</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/brisbane/milton/</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>storage milton</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>/locations/milton/</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>5. Rescue: remainder</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Suburb page</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>/self-storage/brisbane/indooroopilly/</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/brisbane/indooroopilly/</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>storage indooroopilly</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>/locations/indooroopilly/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>5. Rescue: remainder</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Suburb page</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>/self-storage/sydney/northern-beaches/</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/sydney/northern-beaches/</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>storage northern beaches</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>/locations/northern-beaches/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>5. Rescue: remainder</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Suburb page</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>/self-storage/sydney/burwood/</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/sydney/burwood/</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>storage burwood</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>/locations/burwood/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>5. Rescue: remainder</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Suburb page</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>/self-storage/brisbane/caboolture/</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/brisbane/caboolture/</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>storage caboolture</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>/locations/caboolture/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>5. Rescue: remainder</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Suburb page</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>/self-storage/central-coast/maitland/</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/central-coast/maitland/</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>storage maitland</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>/locations/maitland/</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>5. Rescue: remainder</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Suburb page</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>/self-storage/sydney/waterloo/</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/sydney/waterloo/</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>storage waterloo</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>/locations/waterloo/</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>5. Rescue: remainder</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Suburb page</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>/self-storage/sydney/st-marys/</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/sydney/st-marys/</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>storage st marys</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>/locations/st-marys/</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>5. Rescue: remainder</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Suburb page</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>/self-storage/melbourne/clayton/</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/melbourne/clayton/</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>storage clayton</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>/locations/clayton/</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>5. Rescue: remainder</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Suburb page</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>/self-storage/sydney/manly/</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/sydney/manly/</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>storage manly</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>/locations/manly/</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>5. Rescue: remainder</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Suburb page</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>/self-storage/central-coast/morisset/</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/central-coast/morisset/</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>storage morisset</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>/locations/morisset/</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>5. Rescue: remainder</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Suburb page</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>/self-storage/sydney/camperdown/</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/sydney/camperdown/</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>storage camperdown</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>/locations/camperdown/</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>5. Rescue: remainder</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Suburb page</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>/self-storage/sydney/rosebery/</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/sydney/rosebery/</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>storage rosebery</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>/locations/rosebery/</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>5. Rescue: remainder</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Suburb page</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>/self-storage/brisbane/coorparoo/</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/brisbane/coorparoo/</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>storage coorparoo</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>/locations/coorparoo/</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>5. Rescue: remainder</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Suburb page</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>/self-storage/melbourne/collingwood/</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/melbourne/collingwood/</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>storage collingwood</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>/locations/collingwood/</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>6. Format pages</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Format page</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>/storage-pods/</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/storage-pods/</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>storage pods</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>6. Format pages</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Format page</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>/mobile-storage/</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/mobile-storage/</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>mobile storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>6. Format pages</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Format page</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>/portable-storage-containers/</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/portable-storage-containers/</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>portable storage containers</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>6. Format pages</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Format page</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>/moving-pods/</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/moving-pods/</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>moving pods</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>6. Format pages</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Format page</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>/storage-size-calculator/</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/storage-size-calculator/</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>storage size calculator</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>6. Format pages</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Format page</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>/container-sizes/</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/container-sizes/</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>pods sizes</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>7. Interstate routes</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Route page</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>/moving/sydney-to-melbourne/</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/moving/sydney-to-melbourne/</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>removalists sydney to melbourne</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>7. Interstate routes</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Route page</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>/moving/sydney-to-brisbane/</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/moving/sydney-to-brisbane/</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>removalists sydney to brisbane</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>7. Interstate routes</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Route page</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>/moving/sydney-to-adelaide/</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/moving/sydney-to-adelaide/</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>removalists sydney to adelaide</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>7. Interstate routes</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Route page</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>/moving/sydney-to-gold-coast/</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/moving/sydney-to-gold-coast/</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>removalists sydney to gold coast</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>7. Interstate routes</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Route page</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>/moving/melbourne-to-sydney/</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/moving/melbourne-to-sydney/</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>removalists melbourne to sydney</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>7. Interstate routes</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Route page</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>/moving/melbourne-to-brisbane/</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/moving/melbourne-to-brisbane/</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>removalists melbourne to brisbane</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>7. Interstate routes</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Route page</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>/moving/melbourne-to-adelaide/</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/moving/melbourne-to-adelaide/</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>removalists melbourne to adelaide</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>7. Interstate routes</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Route page</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>/moving/melbourne-to-gold-coast/</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/moving/melbourne-to-gold-coast/</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>removalists melbourne to gold coast</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>7. Interstate routes</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Route page</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>/moving/brisbane-to-sydney/</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/moving/brisbane-to-sydney/</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>removalists brisbane to sydney</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>7. Interstate routes</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Route page</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>/moving/brisbane-to-melbourne/</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/moving/brisbane-to-melbourne/</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>removalists brisbane to melbourne</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>7. Interstate routes</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Route page</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>/moving/brisbane-to-adelaide/</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/moving/brisbane-to-adelaide/</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>removalists brisbane to adelaide</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>7. Interstate routes</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Route page</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>/moving/brisbane-to-gold-coast/</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/moving/brisbane-to-gold-coast/</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>removalists brisbane to gold coast</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>7. Interstate routes</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Route page</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>/moving/adelaide-to-sydney/</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/moving/adelaide-to-sydney/</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>removalists adelaide to sydney</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>7. Interstate routes</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Route page</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>/moving/adelaide-to-melbourne/</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/moving/adelaide-to-melbourne/</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>removalists adelaide to melbourne</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>7. Interstate routes</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Route page</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>/moving/adelaide-to-brisbane/</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/moving/adelaide-to-brisbane/</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>removalists adelaide to brisbane</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>7. Interstate routes</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Route page</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>/moving/adelaide-to-gold-coast/</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/moving/adelaide-to-gold-coast/</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>removalists adelaide to gold coast</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>7. Interstate routes</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Route page</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>/moving/gold-coast-to-sydney/</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/moving/gold-coast-to-sydney/</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>removalists gold coast to sydney</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>7. Interstate routes</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Route page</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>/moving/gold-coast-to-melbourne/</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/moving/gold-coast-to-melbourne/</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>removalists gold coast to melbourne</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>7. Interstate routes</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Route page</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>/moving/gold-coast-to-brisbane/</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/moving/gold-coast-to-brisbane/</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>removalists gold coast to brisbane</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>7. Interstate routes</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Route page</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>/moving/gold-coast-to-adelaide/</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/moving/gold-coast-to-adelaide/</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>removalists gold coast to adelaide</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>8. Box shop</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Boxes</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>/moving-boxes/</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/moving-boxes/</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>moving boxes</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>18 x /boxes/* pages 301 here</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>8. Box shop</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Boxes</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>/moving-boxes/brisbane/</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/moving-boxes/brisbane/</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>moving boxes brisbane</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>18 x /boxes/* pages 301 here</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>8. Box shop</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Boxes</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>/packing-supplies/</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/packing-supplies/</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>packing supplies</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>18 x /boxes/* pages 301 here</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>8. Box shop</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Boxes</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>/box-shop/</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/box-shop/</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>box shop</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>18 x /boxes/* pages 301 here</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>9. Comparison and trust</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Comparison</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>/compare/mobile-storage-vs-self-storage/</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/compare/mobile-storage-vs-self-storage/</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>mobile storage vs self storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>9. Comparison and trust</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Comparison</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>/compare/storage-pods-vs-storage-unit/</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/compare/storage-pods-vs-storage-unit/</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>storage unit vs pods</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>9. Comparison and trust</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Comparison</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>/compare/moving-pods-vs-truck-hire/</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/compare/moving-pods-vs-truck-hire/</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>moving pods vs truck</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>9. Comparison and trust</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Comparison</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>/compare/portabox-vs-taxibox/</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/compare/portabox-vs-taxibox/</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>portabox vs taxibox</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>9. Comparison and trust</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Trust</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>/reviews/</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/reviews/</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>portabox reviews</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>9. Comparison and trust</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Trust</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>/formerly-pods-australia/</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/formerly-pods-australia/</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>auspods</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>10. Consolidation review</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>/locations/melbourne/</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/melbourne/</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>/locations/melbourne/</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>10. Consolidation review</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>/locations/mornington/</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/mornington/</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>/locations/mornington/</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>10. Consolidation review</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>/locations/penrith/</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/penrith/</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>/locations/penrith/</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>10. Consolidation review</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>/locations/burleigh/</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/burleigh/</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>/locations/burleigh/</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>10. Consolidation review</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>/locations/port-melbourne/</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/port-melbourne/</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>/locations/port-melbourne/</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>10. Consolidation review</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>/locations/belmont/</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/belmont/</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>/locations/belmont/</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>10. Consolidation review</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>/locations/south-melbourne/</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/south-melbourne/</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>/locations/south-melbourne/</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>10. Consolidation review</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>/locations/tullamarine/</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/tullamarine/</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>/locations/tullamarine/</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>10. Consolidation review</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>/locations/moorabbin/</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/moorabbin/</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>/locations/moorabbin/</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>10. Consolidation review</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>/locations/yatala/</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/yatala/</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>/locations/yatala/</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>10. Consolidation review</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>/locations/capalaba/</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/capalaba/</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>/locations/capalaba/</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>10. Consolidation review</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>/locations/north-sydney/</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/north-sydney/</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>/locations/north-sydney/</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>10. Consolidation review</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>/locations/fremantle/</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/fremantle/</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>/locations/fremantle/</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>10. Consolidation review</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>/locations/brookvale/</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/brookvale/</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>/locations/brookvale/</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>10. Consolidation review</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>/locations/marrickville/</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/marrickville/</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>/locations/marrickville/</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>10. Consolidation review</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>/locations/eastern-suburbs/</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/eastern-suburbs/</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>/locations/eastern-suburbs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>10. Consolidation review</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>/locations/kensington/</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/kensington/</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>/locations/kensington/</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>10. Consolidation review</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>/locations/unanderra/</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/unanderra/</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>/locations/unanderra/</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>10. Consolidation review</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>/locations/north-melbourne/</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/north-melbourne/</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>/locations/north-melbourne/</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>10. Consolidation review</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>/locations/chermside/</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/chermside/</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>/locations/chermside/</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>10. Consolidation review</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>/locations/gladesville/</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/gladesville/</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>/locations/gladesville/</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>10. Consolidation review</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>/locations/altona/</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/altona/</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>/locations/altona/</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>10. Consolidation review</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>/locations/ormeau/</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/ormeau/</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>/locations/ormeau/</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>10. Consolidation review</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>/locations/aspley/</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/aspley/</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>/locations/aspley/</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>10. Consolidation review</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>/locations/brendale/</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/brendale/</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>/locations/brendale/</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>10. Consolidation review</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>/locations/hawthorn/</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/hawthorn/</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>/locations/hawthorn/</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>10. Consolidation review</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>/locations/rozelle/</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/rozelle/</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>/locations/rozelle/</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>10. Consolidation review</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>/locations/balmain/</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/balmain/</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>/locations/balmain/</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>
--- a/Portabox-SEO-Build-Sheet.xlsx
+++ b/Portabox-SEO-Build-Sheet.xlsx
@@ -5,7 +5,6 @@
   <sheets>
     <sheet state="visible" name="Read me first" sheetId="1" r:id="rId5"/>
     <sheet state="visible" name="Build sheet" sheetId="2" r:id="rId6"/>
-    <sheet name="Live links" sheetId="3" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">'Build sheet'!$A$1:$M$127</definedName>
@@ -3002,7 +3001,9 @@
     <col customWidth="1" min="11" max="11" width="26.0"/>
     <col customWidth="1" min="12" max="12" width="24.0"/>
     <col customWidth="1" min="13" max="13" width="78.0"/>
-    <col customWidth="1" min="14" max="26" width="8.71"/>
+    <col customWidth="1" min="14" max="14" width="62.0"/>
+    <col customWidth="1" min="15" max="15" width="14.0"/>
+    <col customWidth="1" min="16" max="26" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="30.0" customHeight="1">
@@ -3045,6 +3046,16 @@
       <c r="M1" s="4" t="s">
         <v>33</v>
       </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Full link</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
@@ -3079,6 +3090,11 @@
       </c>
       <c r="M2" s="10" t="s">
         <v>62</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Not a page</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -3113,6 +3129,11 @@
       <c r="M3" s="10" t="s">
         <v>62</v>
       </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Not a page</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="s">
@@ -3146,6 +3167,11 @@
       <c r="M4" s="10" t="s">
         <v>62</v>
       </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Not a page</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
@@ -3179,6 +3205,11 @@
       <c r="M5" s="10" t="s">
         <v>62</v>
       </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Not a page</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="s">
@@ -3212,6 +3243,16 @@
       <c r="M6" s="14" t="s">
         <v>74</v>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/brisbane/</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="s">
@@ -3245,6 +3286,16 @@
       <c r="M7" s="14" t="s">
         <v>78</v>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/sydney/</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="s">
@@ -3278,6 +3329,16 @@
       <c r="M8" s="14" t="s">
         <v>82</v>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/melbourne/</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="s">
@@ -3310,6 +3371,16 @@
       <c r="L9" s="11"/>
       <c r="M9" s="14" t="s">
         <v>86</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/adelaide/</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -3338,6 +3409,16 @@
       <c r="M10" s="14" t="s">
         <v>90</v>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/robots.txt</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="s">
@@ -3365,6 +3446,16 @@
       <c r="M11" s="14" t="s">
         <v>92</v>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/sitemap.xml</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="s">
@@ -3392,6 +3483,11 @@
       <c r="M12" s="14" t="s">
         <v>94</v>
       </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Not a page</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="s">
@@ -3425,6 +3521,16 @@
       <c r="M13" s="18" t="s">
         <v>99</v>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/brisbane/</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="s">
@@ -3458,6 +3564,16 @@
       <c r="M14" s="18" t="s">
         <v>99</v>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/sydney/</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="s">
@@ -3491,6 +3607,16 @@
       <c r="M15" s="18" t="s">
         <v>99</v>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/melbourne/</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="s">
@@ -3523,6 +3649,16 @@
       <c r="L16" s="15"/>
       <c r="M16" s="18" t="s">
         <v>99</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/adelaide/</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -3555,6 +3691,16 @@
       <c r="M17" s="18" t="s">
         <v>99</v>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/gold-coast/</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="15" t="s">
@@ -3586,6 +3732,16 @@
       <c r="M18" s="18" t="s">
         <v>99</v>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/central-coast/</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="s">
@@ -3619,6 +3775,16 @@
       <c r="M19" s="18" t="s">
         <v>112</v>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/newcastle/</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="15" t="s">
@@ -3652,6 +3818,16 @@
       <c r="M20" s="18" t="s">
         <v>112</v>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/wollongong/</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="19" t="s">
@@ -3689,6 +3865,16 @@
       <c r="M21" s="22" t="s">
         <v>121</v>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/central-coast/west-gosford/</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="19" t="s">
@@ -3726,6 +3912,16 @@
       <c r="M22" s="22" t="s">
         <v>126</v>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/melbourne/hoppers-crossing/</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="19" t="s">
@@ -3763,6 +3959,16 @@
       <c r="M23" s="22" t="s">
         <v>130</v>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/melbourne/box-hill/</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="19" t="s">
@@ -3800,6 +4006,16 @@
       <c r="M24" s="22" t="s">
         <v>135</v>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/adelaide/port-adelaide/</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="19" t="s">
@@ -3837,6 +4053,16 @@
       <c r="M25" s="22" t="s">
         <v>140</v>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/brisbane/ipswich/</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="19" t="s">
@@ -3874,6 +4100,16 @@
       <c r="M26" s="22" t="s">
         <v>144</v>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/sydney/blacktown/</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="19" t="s">
@@ -3911,6 +4147,16 @@
       <c r="M27" s="22" t="s">
         <v>148</v>
       </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/gold-coast/tweed-heads/</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="19" t="s">
@@ -3948,6 +4194,16 @@
       <c r="M28" s="22" t="s">
         <v>152</v>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/sydney/castle-hill/</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="19" t="s">
@@ -3985,6 +4241,16 @@
       <c r="M29" s="22" t="s">
         <v>156</v>
       </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/brisbane/browns-plains/</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="19" t="s">
@@ -4022,6 +4288,16 @@
       <c r="M30" s="22" t="s">
         <v>160</v>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/melbourne/pakenham/</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="19" t="s">
@@ -4059,6 +4335,16 @@
       <c r="M31" s="22" t="s">
         <v>165</v>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/central-coast/rutherford/</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="19" t="s">
@@ -4096,6 +4382,16 @@
       <c r="M32" s="22" t="s">
         <v>169</v>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/sydney/artarmon/</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="19" t="s">
@@ -4133,6 +4429,16 @@
       <c r="M33" s="22" t="s">
         <v>173</v>
       </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/gold-coast/robina/</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="19" t="s">
@@ -4170,6 +4476,16 @@
       <c r="M34" s="22" t="s">
         <v>178</v>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/CHECK/richmond/</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="19" t="s">
@@ -4207,6 +4523,16 @@
       <c r="M35" s="22" t="s">
         <v>182</v>
       </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/CHECK/queanbeyan/</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="19" t="s">
@@ -4244,6 +4570,16 @@
       <c r="M36" s="22" t="s">
         <v>186</v>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/sydney/alexandria/</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="19" t="s">
@@ -4281,6 +4617,16 @@
       <c r="M37" s="22" t="s">
         <v>190</v>
       </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/sydney/dee-why/</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="19" t="s">
@@ -4318,6 +4664,16 @@
       <c r="M38" s="22" t="s">
         <v>194</v>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/melbourne/cheltenham/</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="19" t="s">
@@ -4355,6 +4711,16 @@
       <c r="M39" s="22" t="s">
         <v>198</v>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/melbourne/carrum-downs/</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="19" t="s">
@@ -4392,6 +4758,16 @@
       <c r="M40" s="22" t="s">
         <v>202</v>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/gold-coast/currumbin/</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="19" t="s">
@@ -4429,6 +4805,16 @@
       <c r="M41" s="22" t="s">
         <v>206</v>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/sydney/hornsby/</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="19" t="s">
@@ -4466,6 +4852,16 @@
       <c r="M42" s="22" t="s">
         <v>210</v>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/CHECK/springwood/</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="19" t="s">
@@ -4503,6 +4899,16 @@
       <c r="M43" s="22" t="s">
         <v>214</v>
       </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/sydney/chatswood/</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="19" t="s">
@@ -4540,6 +4946,16 @@
       <c r="M44" s="22" t="s">
         <v>218</v>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/brisbane/logan/</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="19" t="s">
@@ -4577,6 +4993,16 @@
       <c r="M45" s="22" t="s">
         <v>222</v>
       </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/CHECK/mitchell/</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="19" t="s">
@@ -4614,6 +5040,16 @@
       <c r="M46" s="22" t="s">
         <v>226</v>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/gold-coast/nerang/</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="19" t="s">
@@ -4651,6 +5087,16 @@
       <c r="M47" s="22" t="s">
         <v>231</v>
       </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/gold-coast/hope-island/</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="19" t="s">
@@ -4688,6 +5134,16 @@
       <c r="M48" s="22" t="s">
         <v>235</v>
       </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/sydney/bondi-junction/</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="19" t="s">
@@ -4725,6 +5181,16 @@
       <c r="M49" s="22" t="s">
         <v>239</v>
       </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/brisbane/milton/</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="19" t="s">
@@ -4762,6 +5228,16 @@
       <c r="M50" s="22" t="s">
         <v>243</v>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/brisbane/indooroopilly/</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="19" t="s">
@@ -4799,6 +5275,16 @@
       <c r="M51" s="22" t="s">
         <v>247</v>
       </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/sydney/northern-beaches/</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="19" t="s">
@@ -4836,6 +5322,16 @@
       <c r="M52" s="22" t="s">
         <v>251</v>
       </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/sydney/burwood/</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="19" t="s">
@@ -4873,6 +5369,16 @@
       <c r="M53" s="22" t="s">
         <v>255</v>
       </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/brisbane/caboolture/</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="19" t="s">
@@ -4910,6 +5416,16 @@
       <c r="M54" s="22" t="s">
         <v>259</v>
       </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/central-coast/maitland/</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="19" t="s">
@@ -4947,6 +5463,16 @@
       <c r="M55" s="22" t="s">
         <v>263</v>
       </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/sydney/waterloo/</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="19" t="s">
@@ -4984,6 +5510,16 @@
       <c r="M56" s="22" t="s">
         <v>267</v>
       </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/sydney/st-marys/</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="19" t="s">
@@ -5021,6 +5557,16 @@
       <c r="M57" s="22" t="s">
         <v>271</v>
       </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/melbourne/clayton/</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="19" t="s">
@@ -5058,6 +5604,16 @@
       <c r="M58" s="22" t="s">
         <v>275</v>
       </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/sydney/manly/</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="19" t="s">
@@ -5095,6 +5651,16 @@
       <c r="M59" s="22" t="s">
         <v>279</v>
       </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/central-coast/morisset/</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="19" t="s">
@@ -5132,6 +5698,16 @@
       <c r="M60" s="22" t="s">
         <v>283</v>
       </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/sydney/camperdown/</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="19" t="s">
@@ -5169,6 +5745,16 @@
       <c r="M61" s="22" t="s">
         <v>287</v>
       </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/sydney/rosebery/</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="19" t="s">
@@ -5206,6 +5792,16 @@
       <c r="M62" s="22" t="s">
         <v>291</v>
       </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/brisbane/coorparoo/</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="19" t="s">
@@ -5242,6 +5838,16 @@
       </c>
       <c r="M63" s="22" t="s">
         <v>295</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/self-storage/melbourne/collingwood/</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
       </c>
     </row>
     <row r="64" ht="15.75" customHeight="1">
@@ -5274,6 +5880,16 @@
       <c r="M64" s="18" t="s">
         <v>300</v>
       </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/storage-pods/</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="15" t="s">
@@ -5305,6 +5921,16 @@
       <c r="M65" s="18" t="s">
         <v>303</v>
       </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/mobile-storage/</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="15" t="s">
@@ -5336,6 +5962,16 @@
       <c r="M66" s="18" t="s">
         <v>306</v>
       </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/portable-storage-containers/</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="15" t="s">
@@ -5366,6 +6002,16 @@
       <c r="L67" s="15"/>
       <c r="M67" s="18" t="s">
         <v>309</v>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/moving-pods/</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
       </c>
     </row>
     <row r="68" ht="15.75" customHeight="1">
@@ -5396,6 +6042,16 @@
       <c r="M68" s="18" t="s">
         <v>312</v>
       </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/storage-size-calculator/</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="15" t="s">
@@ -5425,6 +6081,16 @@
       <c r="M69" s="18" t="s">
         <v>315</v>
       </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/container-sizes/</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="15" t="s">
@@ -5455,6 +6121,16 @@
       <c r="L70" s="15"/>
       <c r="M70" s="18" t="s">
         <v>320</v>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/moving/sydney-to-melbourne/</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1">
@@ -5485,6 +6161,16 @@
       <c r="M71" s="18" t="s">
         <v>320</v>
       </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/moving/sydney-to-brisbane/</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="15" t="s">
@@ -5514,6 +6200,16 @@
       <c r="M72" s="18" t="s">
         <v>320</v>
       </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/moving/sydney-to-adelaide/</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="15" t="s">
@@ -5543,6 +6239,16 @@
       <c r="M73" s="18" t="s">
         <v>320</v>
       </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/moving/sydney-to-gold-coast/</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="15" t="s">
@@ -5572,6 +6278,16 @@
       <c r="M74" s="18" t="s">
         <v>320</v>
       </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/moving/melbourne-to-sydney/</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="15" t="s">
@@ -5601,6 +6317,16 @@
       <c r="M75" s="18" t="s">
         <v>320</v>
       </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/moving/melbourne-to-brisbane/</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="15" t="s">
@@ -5630,6 +6356,16 @@
       <c r="M76" s="18" t="s">
         <v>320</v>
       </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/moving/melbourne-to-adelaide/</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="15" t="s">
@@ -5659,6 +6395,16 @@
       <c r="M77" s="18" t="s">
         <v>320</v>
       </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/moving/melbourne-to-gold-coast/</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="15" t="s">
@@ -5688,6 +6434,16 @@
       <c r="M78" s="18" t="s">
         <v>320</v>
       </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/moving/brisbane-to-sydney/</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="15" t="s">
@@ -5717,6 +6473,16 @@
       <c r="M79" s="18" t="s">
         <v>320</v>
       </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/moving/brisbane-to-melbourne/</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="15" t="s">
@@ -5746,6 +6512,16 @@
       <c r="M80" s="18" t="s">
         <v>320</v>
       </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/moving/brisbane-to-adelaide/</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="15" t="s">
@@ -5775,6 +6551,16 @@
       <c r="M81" s="18" t="s">
         <v>320</v>
       </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/moving/brisbane-to-gold-coast/</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="15" t="s">
@@ -5804,6 +6590,16 @@
       <c r="M82" s="18" t="s">
         <v>320</v>
       </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/moving/adelaide-to-sydney/</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="15" t="s">
@@ -5833,6 +6629,16 @@
       <c r="M83" s="18" t="s">
         <v>320</v>
       </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/moving/adelaide-to-melbourne/</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="15" t="s">
@@ -5862,6 +6668,16 @@
       <c r="M84" s="18" t="s">
         <v>320</v>
       </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/moving/adelaide-to-brisbane/</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="15" t="s">
@@ -5891,6 +6707,16 @@
       <c r="M85" s="18" t="s">
         <v>320</v>
       </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/moving/adelaide-to-gold-coast/</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="15" t="s">
@@ -5920,6 +6746,16 @@
       <c r="M86" s="18" t="s">
         <v>320</v>
       </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/moving/gold-coast-to-sydney/</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="15" t="s">
@@ -5949,6 +6785,16 @@
       <c r="M87" s="18" t="s">
         <v>320</v>
       </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/moving/gold-coast-to-melbourne/</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="15" t="s">
@@ -5978,6 +6824,16 @@
       <c r="M88" s="18" t="s">
         <v>320</v>
       </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/moving/gold-coast-to-brisbane/</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="15" t="s">
@@ -6007,6 +6863,16 @@
       <c r="M89" s="18" t="s">
         <v>320</v>
       </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/moving/gold-coast-to-adelaide/</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="11" t="s">
@@ -6039,6 +6905,16 @@
       <c r="L90" s="11"/>
       <c r="M90" s="14" t="s">
         <v>364</v>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/moving-boxes/</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
       </c>
     </row>
     <row r="91" ht="15.75" customHeight="1">
@@ -6071,6 +6947,16 @@
       <c r="M91" s="14" t="s">
         <v>367</v>
       </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/moving-boxes/brisbane/</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="11" t="s">
@@ -6102,6 +6988,16 @@
       <c r="M92" s="14" t="s">
         <v>370</v>
       </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/packing-supplies/</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="11" t="s">
@@ -6133,6 +7029,16 @@
       <c r="M93" s="14" t="s">
         <v>373</v>
       </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/box-shop/</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="15" t="s">
@@ -6162,6 +7068,16 @@
       <c r="M94" s="18" t="s">
         <v>378</v>
       </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/compare/mobile-storage-vs-self-storage/</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="15" t="s">
@@ -6189,6 +7105,16 @@
       <c r="K95" s="16"/>
       <c r="L95" s="15"/>
       <c r="M95" s="18"/>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/compare/storage-pods-vs-storage-unit/</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="15" t="s">
@@ -6216,6 +7142,16 @@
       <c r="K96" s="16"/>
       <c r="L96" s="15"/>
       <c r="M96" s="18"/>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/compare/moving-pods-vs-truck-hire/</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="15" t="s">
@@ -6245,6 +7181,16 @@
       <c r="M97" s="18" t="s">
         <v>385</v>
       </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/compare/portabox-vs-taxibox/</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="6" t="s">
@@ -6274,6 +7220,16 @@
       <c r="M98" s="10" t="s">
         <v>389</v>
       </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/reviews/</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="6" t="s">
@@ -6305,6 +7261,16 @@
       <c r="M99" s="10" t="s">
         <v>392</v>
       </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/formerly-pods-australia/</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="23" t="s">
@@ -6338,6 +7304,16 @@
       <c r="M100" s="26" t="s">
         <v>397</v>
       </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/melbourne/</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="23" t="s">
@@ -6371,6 +7347,16 @@
       <c r="M101" s="26" t="s">
         <v>399</v>
       </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/mornington/</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="23" t="s">
@@ -6404,6 +7390,16 @@
       <c r="M102" s="26" t="s">
         <v>401</v>
       </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/penrith/</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="23" t="s">
@@ -6437,6 +7433,16 @@
       <c r="M103" s="26" t="s">
         <v>403</v>
       </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/burleigh/</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="23" t="s">
@@ -6470,6 +7476,16 @@
       <c r="M104" s="26" t="s">
         <v>405</v>
       </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/port-melbourne/</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="23" t="s">
@@ -6503,6 +7519,16 @@
       <c r="M105" s="26" t="s">
         <v>407</v>
       </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/belmont/</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="23" t="s">
@@ -6536,6 +7562,16 @@
       <c r="M106" s="26" t="s">
         <v>409</v>
       </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/south-melbourne/</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="23" t="s">
@@ -6569,6 +7605,16 @@
       <c r="M107" s="26" t="s">
         <v>411</v>
       </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/tullamarine/</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="23" t="s">
@@ -6602,6 +7648,16 @@
       <c r="M108" s="26" t="s">
         <v>413</v>
       </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/moorabbin/</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="23" t="s">
@@ -6635,6 +7691,16 @@
       <c r="M109" s="26" t="s">
         <v>415</v>
       </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/yatala/</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="23" t="s">
@@ -6668,6 +7734,16 @@
       <c r="M110" s="26" t="s">
         <v>417</v>
       </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/capalaba/</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="23" t="s">
@@ -6701,6 +7777,16 @@
       <c r="M111" s="26" t="s">
         <v>419</v>
       </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/north-sydney/</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="23" t="s">
@@ -6734,6 +7820,16 @@
       <c r="M112" s="26" t="s">
         <v>421</v>
       </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/fremantle/</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="23" t="s">
@@ -6767,6 +7863,16 @@
       <c r="M113" s="26" t="s">
         <v>423</v>
       </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/brookvale/</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="23" t="s">
@@ -6800,6 +7906,16 @@
       <c r="M114" s="26" t="s">
         <v>425</v>
       </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/marrickville/</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="23" t="s">
@@ -6833,6 +7949,16 @@
       <c r="M115" s="26" t="s">
         <v>427</v>
       </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/eastern-suburbs/</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="23" t="s">
@@ -6866,6 +7992,16 @@
       <c r="M116" s="26" t="s">
         <v>429</v>
       </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/kensington/</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="23" t="s">
@@ -6899,6 +8035,16 @@
       <c r="M117" s="26" t="s">
         <v>431</v>
       </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/unanderra/</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="23" t="s">
@@ -6932,6 +8078,16 @@
       <c r="M118" s="26" t="s">
         <v>433</v>
       </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/north-melbourne/</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="23" t="s">
@@ -6965,6 +8121,16 @@
       <c r="M119" s="26" t="s">
         <v>435</v>
       </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/chermside/</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="23" t="s">
@@ -6998,6 +8164,16 @@
       <c r="M120" s="26" t="s">
         <v>437</v>
       </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/gladesville/</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="23" t="s">
@@ -7031,6 +8207,16 @@
       <c r="M121" s="26" t="s">
         <v>439</v>
       </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/altona/</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="23" t="s">
@@ -7064,6 +8250,16 @@
       <c r="M122" s="26" t="s">
         <v>441</v>
       </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/ormeau/</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="23" t="s">
@@ -7097,6 +8293,16 @@
       <c r="M123" s="26" t="s">
         <v>443</v>
       </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/aspley/</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="23" t="s">
@@ -7130,6 +8336,16 @@
       <c r="M124" s="26" t="s">
         <v>445</v>
       </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/brendale/</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="23" t="s">
@@ -7163,6 +8379,16 @@
       <c r="M125" s="26" t="s">
         <v>447</v>
       </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/hawthorn/</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="23" t="s">
@@ -7196,6 +8422,16 @@
       <c r="M126" s="26" t="s">
         <v>449</v>
       </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/rozelle/</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="23" t="s">
@@ -7228,6 +8464,16 @@
       <c r="L127" s="23"/>
       <c r="M127" s="26" t="s">
         <v>451</v>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>https://portabox-website.vercel.app/locations/balmain/</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>Not built yet</t>
+        </is>
       </c>
     </row>
     <row r="128" ht="15.75" customHeight="1"/>
@@ -8115,4970 +9361,4 @@
   <pageSetup orientation="landscape"/>
   <drawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <cols>
-    <col min="1" max="1" width="5"/>
-    <col min="2" max="2" width="24"/>
-    <col min="3" max="3" width="18"/>
-    <col min="4" max="4" width="40"/>
-    <col min="5" max="5" width="64"/>
-    <col min="6" max="6" width="14"/>
-    <col min="7" max="7" width="30"/>
-    <col min="8" max="8" width="34"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Batch</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Page type</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Path</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Full link</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Target keyword</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Old URL to 301</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1. Quick wins, no build</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Google Business Profile</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>GBP: Brisbane depot</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Not a page</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>storage near me</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>1. Quick wins, no build</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Google Business Profile</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>GBP: Sydney depot</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Not a page</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>storage near me</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1. Quick wins, no build</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Google Business Profile</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>GBP: Melbourne depot</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Not a page</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>storage near me</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1. Quick wins, no build</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Google Business Profile</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>GBP: Adelaide depot</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Not a page</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>storage near me</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1. Quick wins, no build</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Title fix</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>/self-storage/brisbane/</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/brisbane/</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Live</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>self storage brisbane</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Storage &amp; Moving Containers in South East Queensland</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1. Quick wins, no build</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Title fix</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>/self-storage/sydney/</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/sydney/</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Live</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>self storage sydney</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Storage &amp; Moving Containers in Greater Sydney</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>1. Quick wins, no build</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Title fix</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>/self-storage/melbourne/</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/melbourne/</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Live</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>self storage melbourne</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Storage &amp; Moving Containers in Victoria</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>1. Quick wins, no build</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Title fix</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>/self-storage/adelaide/</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/adelaide/</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Live</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>self storage adelaide</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Storage &amp; Moving Containers in South Australia</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>1. Quick wins, no build</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Technical</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>robots.txt</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/robots.txt</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Live</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1. Quick wins, no build</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Technical</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>sitemap.xml</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/sitemap.xml</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Live</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1. Quick wins, no build</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Technical</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>JSON-LD schema layer</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Not a page</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2. Region hubs</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Region hub</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>/self-storage/brisbane/</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/brisbane/</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Live</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>storage brisbane</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>/locations/brisbane/ (301 to here)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2. Region hubs</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Region hub</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>/self-storage/sydney/</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/sydney/</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Live</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>self storage sydney</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>/locations/sydney/ (301 to here)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2. Region hubs</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Region hub</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>/self-storage/melbourne/</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/melbourne/</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Live</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>self storage melbourne</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>/locations/melbourne/ (301 to here)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2. Region hubs</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Region hub</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>/self-storage/adelaide/</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/adelaide/</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Live</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>self storage adelaide</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>/locations/adelaide/ (301 to here)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2. Region hubs</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Region hub</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>/self-storage/gold-coast/</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/gold-coast/</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Live</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>self storage gold coast</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>/locations/gold-coast/ (301 to here)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2. Region hubs</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Region hub</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>/self-storage/central-coast/</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/central-coast/</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Live</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>self storage central coast</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>/locations/central-coast/ (301 to here)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2. Region hubs</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Region hub</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>/self-storage/newcastle/</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/newcastle/</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Live</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>self storage newcastle</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2. Region hubs</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Region hub</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>/self-storage/wollongong/</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/wollongong/</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Live</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>self storage wollongong</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>3. Rescue: top 10</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Suburb page</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>/self-storage/central-coast/west-gosford/</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/central-coast/west-gosford/</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>storage west gosford</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>/locations/west-gosford/</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>3. Rescue: top 10</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Suburb page</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>/self-storage/melbourne/hoppers-crossing/</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/melbourne/hoppers-crossing/</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>storage hoppers crossing</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>/locations/hoppers-crossing/</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>3. Rescue: top 10</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Suburb page</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>/self-storage/melbourne/box-hill/</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/melbourne/box-hill/</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>storage box hill</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>/locations/box-hill/</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>3. Rescue: top 10</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Suburb page</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>/self-storage/adelaide/port-adelaide/</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/adelaide/port-adelaide/</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>storage port adelaide</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>/locations/port-adelaide/</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>3. Rescue: top 10</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Suburb page</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>/self-storage/brisbane/ipswich/</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/brisbane/ipswich/</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>storage ipswich</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>/locations/ipswich/</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>3. Rescue: top 10</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Suburb page</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>/self-storage/sydney/blacktown/</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/sydney/blacktown/</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>storage blacktown</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>/locations/blacktown/</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3. Rescue: top 10</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Suburb page</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>/self-storage/gold-coast/tweed-heads/</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/gold-coast/tweed-heads/</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>storage tweed heads</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>/locations/tweed-heads/</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3. Rescue: top 10</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Suburb page</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>/self-storage/sydney/castle-hill/</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/sydney/castle-hill/</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>storage castle hill</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>/locations/castle-hill/</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3. Rescue: top 10</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Suburb page</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>/self-storage/brisbane/browns-plains/</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/brisbane/browns-plains/</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>storage browns plains</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>/locations/browns-plains/</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3. Rescue: top 10</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Suburb page</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>/self-storage/melbourne/pakenham/</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/melbourne/pakenham/</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>storage pakenham</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>/locations/pakenham/</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>4. Rescue: next 16</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Suburb page</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>/self-storage/central-coast/rutherford/</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/central-coast/rutherford/</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>storage rutherford</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>/locations/rutherford/</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>4. Rescue: next 16</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Suburb page</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>/self-storage/sydney/artarmon/</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/sydney/artarmon/</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>storage artarmon</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>/locations/artarmon/</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>4. Rescue: next 16</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Suburb page</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>/self-storage/gold-coast/robina/</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/gold-coast/robina/</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>storage robina</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>/locations/robina/</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>4. Rescue: next 16</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Suburb page</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>/self-storage/CHECK/richmond/</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/CHECK/richmond/</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>storage richmond</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>/locations/richmond/</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4. Rescue: next 16</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Suburb page</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>/self-storage/CHECK/queanbeyan/</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/CHECK/queanbeyan/</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>storage queanbeyan</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>/locations/queanbeyan/</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>4. Rescue: next 16</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Suburb page</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>/self-storage/sydney/alexandria/</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/sydney/alexandria/</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>storage alexandria</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>/locations/alexandria/</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>4. Rescue: next 16</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Suburb page</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>/self-storage/sydney/dee-why/</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/sydney/dee-why/</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>storage dee why</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>/locations/dee-why/</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>4. Rescue: next 16</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Suburb page</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>/self-storage/melbourne/cheltenham/</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/melbourne/cheltenham/</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>storage cheltenham</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>/locations/cheltenham/</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>4. Rescue: next 16</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Suburb page</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>/self-storage/melbourne/carrum-downs/</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/melbourne/carrum-downs/</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>storage carrum downs</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>/locations/carrum-downs/</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>4. Rescue: next 16</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Suburb page</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>/self-storage/gold-coast/currumbin/</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/gold-coast/currumbin/</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>storage currumbin</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>/locations/currumbin/</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>4. Rescue: next 16</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Suburb page</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>/self-storage/sydney/hornsby/</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/sydney/hornsby/</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>storage hornsby</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>/locations/hornsby/</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>4. Rescue: next 16</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Suburb page</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>/self-storage/CHECK/springwood/</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/CHECK/springwood/</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>storage springwood</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>/locations/springwood/</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>4. Rescue: next 16</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Suburb page</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>/self-storage/sydney/chatswood/</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/sydney/chatswood/</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>storage chatswood</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>/locations/chatswood/</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>4. Rescue: next 16</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Suburb page</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>/self-storage/brisbane/logan/</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/brisbane/logan/</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>storage logan</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>/locations/logan/</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>4. Rescue: next 16</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Suburb page</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>/self-storage/CHECK/mitchell/</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/CHECK/mitchell/</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>storage mitchell</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>/locations/mitchell/</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>4. Rescue: next 16</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Suburb page</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>/self-storage/gold-coast/nerang/</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/gold-coast/nerang/</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>storage nerang</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>/locations/nerang/</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>5. Rescue: remainder</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Suburb page</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>/self-storage/gold-coast/hope-island/</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/gold-coast/hope-island/</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>storage hope island</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>/locations/hope-island/</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>5. Rescue: remainder</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Suburb page</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>/self-storage/sydney/bondi-junction/</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/sydney/bondi-junction/</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>storage bondi junction</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>/locations/bondi-junction/</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>5. Rescue: remainder</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Suburb page</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>/self-storage/brisbane/milton/</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/brisbane/milton/</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>storage milton</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>/locations/milton/</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>5. Rescue: remainder</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Suburb page</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>/self-storage/brisbane/indooroopilly/</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/brisbane/indooroopilly/</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>storage indooroopilly</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>/locations/indooroopilly/</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>5. Rescue: remainder</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Suburb page</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>/self-storage/sydney/northern-beaches/</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/sydney/northern-beaches/</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>storage northern beaches</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>/locations/northern-beaches/</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>5. Rescue: remainder</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Suburb page</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>/self-storage/sydney/burwood/</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/sydney/burwood/</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>storage burwood</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>/locations/burwood/</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>5. Rescue: remainder</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Suburb page</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>/self-storage/brisbane/caboolture/</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/brisbane/caboolture/</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>storage caboolture</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>/locations/caboolture/</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>5. Rescue: remainder</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Suburb page</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>/self-storage/central-coast/maitland/</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/central-coast/maitland/</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>storage maitland</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>/locations/maitland/</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>5. Rescue: remainder</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Suburb page</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>/self-storage/sydney/waterloo/</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/sydney/waterloo/</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>storage waterloo</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>/locations/waterloo/</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>5. Rescue: remainder</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Suburb page</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>/self-storage/sydney/st-marys/</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/sydney/st-marys/</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>storage st marys</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>/locations/st-marys/</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>5. Rescue: remainder</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Suburb page</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>/self-storage/melbourne/clayton/</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/melbourne/clayton/</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>storage clayton</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>/locations/clayton/</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>5. Rescue: remainder</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Suburb page</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>/self-storage/sydney/manly/</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/sydney/manly/</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>storage manly</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>/locations/manly/</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>5. Rescue: remainder</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Suburb page</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>/self-storage/central-coast/morisset/</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/central-coast/morisset/</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>storage morisset</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>/locations/morisset/</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>5. Rescue: remainder</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Suburb page</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>/self-storage/sydney/camperdown/</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/sydney/camperdown/</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>storage camperdown</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>/locations/camperdown/</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>5. Rescue: remainder</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Suburb page</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>/self-storage/sydney/rosebery/</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/sydney/rosebery/</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>storage rosebery</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>/locations/rosebery/</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>5. Rescue: remainder</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Suburb page</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>/self-storage/brisbane/coorparoo/</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/brisbane/coorparoo/</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>storage coorparoo</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>/locations/coorparoo/</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>5. Rescue: remainder</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Suburb page</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>/self-storage/melbourne/collingwood/</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/self-storage/melbourne/collingwood/</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>storage collingwood</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>/locations/collingwood/</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>6. Format pages</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Format page</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>/storage-pods/</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/storage-pods/</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>storage pods</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>6. Format pages</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Format page</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>/mobile-storage/</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/mobile-storage/</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>mobile storage</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>6. Format pages</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Format page</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>/portable-storage-containers/</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/portable-storage-containers/</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>portable storage containers</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>6. Format pages</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Format page</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>/moving-pods/</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/moving-pods/</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>moving pods</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>6. Format pages</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Format page</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>/storage-size-calculator/</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/storage-size-calculator/</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>storage size calculator</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>6. Format pages</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Format page</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>/container-sizes/</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/container-sizes/</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Live</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>pods sizes</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>7. Interstate routes</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Route page</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>/moving/sydney-to-melbourne/</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/moving/sydney-to-melbourne/</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>removalists sydney to melbourne</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>7. Interstate routes</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Route page</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>/moving/sydney-to-brisbane/</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/moving/sydney-to-brisbane/</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>removalists sydney to brisbane</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>7. Interstate routes</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Route page</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>/moving/sydney-to-adelaide/</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/moving/sydney-to-adelaide/</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>removalists sydney to adelaide</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>7. Interstate routes</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Route page</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>/moving/sydney-to-gold-coast/</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/moving/sydney-to-gold-coast/</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>removalists sydney to gold coast</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>7. Interstate routes</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Route page</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>/moving/melbourne-to-sydney/</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/moving/melbourne-to-sydney/</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>removalists melbourne to sydney</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>7. Interstate routes</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Route page</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>/moving/melbourne-to-brisbane/</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/moving/melbourne-to-brisbane/</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>removalists melbourne to brisbane</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>7. Interstate routes</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Route page</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>/moving/melbourne-to-adelaide/</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/moving/melbourne-to-adelaide/</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>removalists melbourne to adelaide</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>7. Interstate routes</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Route page</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>/moving/melbourne-to-gold-coast/</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/moving/melbourne-to-gold-coast/</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>removalists melbourne to gold coast</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>7. Interstate routes</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Route page</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>/moving/brisbane-to-sydney/</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/moving/brisbane-to-sydney/</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>removalists brisbane to sydney</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>7. Interstate routes</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Route page</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>/moving/brisbane-to-melbourne/</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/moving/brisbane-to-melbourne/</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>removalists brisbane to melbourne</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>7. Interstate routes</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Route page</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>/moving/brisbane-to-adelaide/</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/moving/brisbane-to-adelaide/</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>removalists brisbane to adelaide</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>7. Interstate routes</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Route page</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>/moving/brisbane-to-gold-coast/</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/moving/brisbane-to-gold-coast/</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>removalists brisbane to gold coast</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>7. Interstate routes</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Route page</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>/moving/adelaide-to-sydney/</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/moving/adelaide-to-sydney/</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>removalists adelaide to sydney</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>7. Interstate routes</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Route page</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>/moving/adelaide-to-melbourne/</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/moving/adelaide-to-melbourne/</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>removalists adelaide to melbourne</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>7. Interstate routes</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Route page</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>/moving/adelaide-to-brisbane/</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/moving/adelaide-to-brisbane/</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>removalists adelaide to brisbane</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>7. Interstate routes</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Route page</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>/moving/adelaide-to-gold-coast/</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/moving/adelaide-to-gold-coast/</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>removalists adelaide to gold coast</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>7. Interstate routes</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Route page</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>/moving/gold-coast-to-sydney/</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/moving/gold-coast-to-sydney/</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>removalists gold coast to sydney</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>7. Interstate routes</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Route page</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>/moving/gold-coast-to-melbourne/</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/moving/gold-coast-to-melbourne/</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>removalists gold coast to melbourne</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>7. Interstate routes</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Route page</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>/moving/gold-coast-to-brisbane/</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/moving/gold-coast-to-brisbane/</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>removalists gold coast to brisbane</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>7. Interstate routes</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Route page</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>/moving/gold-coast-to-adelaide/</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/moving/gold-coast-to-adelaide/</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>removalists gold coast to adelaide</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>8. Box shop</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Boxes</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>/moving-boxes/</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/moving-boxes/</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>moving boxes</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>18 x /boxes/* pages 301 here</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>8. Box shop</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Boxes</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>/moving-boxes/brisbane/</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/moving-boxes/brisbane/</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>moving boxes brisbane</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>18 x /boxes/* pages 301 here</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>8. Box shop</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Boxes</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>/packing-supplies/</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/packing-supplies/</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>packing supplies</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>18 x /boxes/* pages 301 here</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>8. Box shop</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Boxes</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>/box-shop/</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/box-shop/</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>box shop</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>18 x /boxes/* pages 301 here</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>9. Comparison and trust</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Comparison</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>/compare/mobile-storage-vs-self-storage/</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/compare/mobile-storage-vs-self-storage/</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>mobile storage vs self storage</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>9. Comparison and trust</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Comparison</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>/compare/storage-pods-vs-storage-unit/</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/compare/storage-pods-vs-storage-unit/</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>storage unit vs pods</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>9. Comparison and trust</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Comparison</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>/compare/moving-pods-vs-truck-hire/</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/compare/moving-pods-vs-truck-hire/</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>moving pods vs truck</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>9. Comparison and trust</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Comparison</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>/compare/portabox-vs-taxibox/</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/compare/portabox-vs-taxibox/</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>portabox vs taxibox</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>9. Comparison and trust</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Trust</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>/reviews/</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/reviews/</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>portabox reviews</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>9. Comparison and trust</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Trust</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>/formerly-pods-australia/</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/formerly-pods-australia/</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>auspods</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>10. Consolidation review</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>/locations/melbourne/</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/locations/melbourne/</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>/locations/melbourne/</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>10. Consolidation review</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>/locations/mornington/</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/locations/mornington/</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>/locations/mornington/</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>10. Consolidation review</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>/locations/penrith/</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/locations/penrith/</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>/locations/penrith/</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>10. Consolidation review</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>/locations/burleigh/</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/locations/burleigh/</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>/locations/burleigh/</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>10. Consolidation review</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>/locations/port-melbourne/</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/locations/port-melbourne/</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>/locations/port-melbourne/</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>10. Consolidation review</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>/locations/belmont/</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/locations/belmont/</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>/locations/belmont/</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>10. Consolidation review</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>/locations/south-melbourne/</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/locations/south-melbourne/</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>/locations/south-melbourne/</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>10. Consolidation review</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>/locations/tullamarine/</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/locations/tullamarine/</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>/locations/tullamarine/</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>10. Consolidation review</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>/locations/moorabbin/</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/locations/moorabbin/</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>/locations/moorabbin/</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>10. Consolidation review</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>/locations/yatala/</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/locations/yatala/</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>/locations/yatala/</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>10. Consolidation review</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>/locations/capalaba/</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/locations/capalaba/</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>/locations/capalaba/</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>10. Consolidation review</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>/locations/north-sydney/</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/locations/north-sydney/</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>/locations/north-sydney/</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>10. Consolidation review</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>/locations/fremantle/</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/locations/fremantle/</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>/locations/fremantle/</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>10. Consolidation review</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>/locations/brookvale/</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/locations/brookvale/</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>/locations/brookvale/</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>10. Consolidation review</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>/locations/marrickville/</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/locations/marrickville/</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>/locations/marrickville/</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>10. Consolidation review</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>/locations/eastern-suburbs/</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/locations/eastern-suburbs/</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>/locations/eastern-suburbs/</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>10. Consolidation review</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>/locations/kensington/</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/locations/kensington/</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>/locations/kensington/</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>10. Consolidation review</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>/locations/unanderra/</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/locations/unanderra/</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>/locations/unanderra/</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>10. Consolidation review</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>/locations/north-melbourne/</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/locations/north-melbourne/</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>/locations/north-melbourne/</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>10. Consolidation review</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>/locations/chermside/</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/locations/chermside/</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>/locations/chermside/</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>10. Consolidation review</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>/locations/gladesville/</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/locations/gladesville/</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>/locations/gladesville/</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>10. Consolidation review</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>/locations/altona/</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/locations/altona/</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>/locations/altona/</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>10. Consolidation review</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>/locations/ormeau/</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/locations/ormeau/</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>/locations/ormeau/</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>10. Consolidation review</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>/locations/aspley/</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/locations/aspley/</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>/locations/aspley/</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>10. Consolidation review</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>/locations/brendale/</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/locations/brendale/</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>/locations/brendale/</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>10. Consolidation review</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>/locations/hawthorn/</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/locations/hawthorn/</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>/locations/hawthorn/</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>10. Consolidation review</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>/locations/rozelle/</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/locations/rozelle/</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>/locations/rozelle/</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>10. Consolidation review</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>/locations/balmain/</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>https://portabox-website.vercel.app/locations/balmain/</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>Not built yet</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>/locations/balmain/</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-</worksheet>
 </file>
--- a/Portabox-SEO-Build-Sheet.xlsx
+++ b/Portabox-SEO-Build-Sheet.xlsx
@@ -3003,7 +3003,8 @@
     <col customWidth="1" min="13" max="13" width="78.0"/>
     <col customWidth="1" min="14" max="14" width="62.0"/>
     <col customWidth="1" min="15" max="15" width="14.0"/>
-    <col customWidth="1" min="16" max="26" width="8.71"/>
+    <col customWidth="1" min="16" max="16" width="86.0"/>
+    <col customWidth="1" min="17" max="26" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="30.0" customHeight="1">
@@ -3056,6 +3057,11 @@
           <t>Status</t>
         </is>
       </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
@@ -3094,6 +3100,11 @@
       <c r="O2" t="inlineStr">
         <is>
           <t>Not a page</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Not a page on this site. These are Google listings and the SEO team said to leave them for now.</t>
         </is>
       </c>
     </row>
@@ -3134,6 +3145,11 @@
           <t>Not a page</t>
         </is>
       </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Not a page on this site. These are Google listings and the SEO team said to leave them for now.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="s">
@@ -3172,6 +3188,11 @@
           <t>Not a page</t>
         </is>
       </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Not a page on this site. These are Google listings and the SEO team said to leave them for now.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
@@ -3208,6 +3229,11 @@
       <c r="O5" t="inlineStr">
         <is>
           <t>Not a page</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Not a page on this site. These are Google listings and the SEO team said to leave them for now.</t>
         </is>
       </c>
     </row>
@@ -3488,6 +3514,11 @@
           <t>Not a page</t>
         </is>
       </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>BUILT, but not as a page: the schema is generated into the head of all 105 pages — Organization everywhere, SelfStorage on each region hub and facility, FAQPage and BreadcrumbList where they apply.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="s">
@@ -4486,6 +4517,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>BLOCKED, needs one decision: this suburb name exists in more than one state, so the page would land under the wrong region hub. Confirm the state and it is a few minutes to build.</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="19" t="s">
@@ -4533,6 +4569,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>BLOCKED, needs one decision: this suburb name exists in more than one state, so the page would land under the wrong region hub. Confirm the state and it is a few minutes to build.</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="19" t="s">
@@ -4862,6 +4903,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>BLOCKED, needs one decision: this suburb name exists in more than one state, so the page would land under the wrong region hub. Confirm the state and it is a few minutes to build.</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="19" t="s">
@@ -5001,6 +5047,11 @@
       <c r="O45" t="inlineStr">
         <is>
           <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>BLOCKED, needs one decision: this suburb name exists in more than one state, so the page would land under the wrong region hub. Confirm the state and it is a few minutes to build.</t>
         </is>
       </c>
     </row>
@@ -7314,6 +7365,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="23" t="s">
@@ -7357,6 +7413,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="23" t="s">
@@ -7400,6 +7461,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="23" t="s">
@@ -7443,6 +7509,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="23" t="s">
@@ -7486,6 +7557,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="23" t="s">
@@ -7529,6 +7605,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="23" t="s">
@@ -7572,6 +7653,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="23" t="s">
@@ -7615,6 +7701,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="23" t="s">
@@ -7658,6 +7749,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="23" t="s">
@@ -7701,6 +7797,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="23" t="s">
@@ -7744,6 +7845,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="23" t="s">
@@ -7787,6 +7893,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="23" t="s">
@@ -7830,6 +7941,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="23" t="s">
@@ -7873,6 +7989,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="23" t="s">
@@ -7916,6 +8037,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="23" t="s">
@@ -7959,6 +8085,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="23" t="s">
@@ -8002,6 +8133,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="23" t="s">
@@ -8045,6 +8181,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="23" t="s">
@@ -8088,6 +8229,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="23" t="s">
@@ -8131,6 +8277,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="23" t="s">
@@ -8174,6 +8325,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="23" t="s">
@@ -8217,6 +8373,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="23" t="s">
@@ -8260,6 +8421,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="23" t="s">
@@ -8303,6 +8469,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="23" t="s">
@@ -8346,6 +8517,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="23" t="s">
@@ -8389,6 +8565,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="23" t="s">
@@ -8432,6 +8613,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="23" t="s">
@@ -8473,6 +8659,11 @@
       <c r="O127" t="inlineStr">
         <is>
           <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
         </is>
       </c>
     </row>

--- a/Portabox-SEO-Build-Sheet.xlsx
+++ b/Portabox-SEO-Build-Sheet.xlsx
@@ -3516,7 +3516,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>BUILT, but not as a page: the schema is generated into the head of all 105 pages — Organization everywhere, SelfStorage on each region hub and facility, FAQPage and BreadcrumbList where they apply.</t>
+          <t>BUILT, but not as a page: the schema is generated into the head of all 127 pages — Organization everywhere, SelfStorage on each region hub and facility, FAQPage and BreadcrumbList where they apply.</t>
         </is>
       </c>
     </row>
@@ -7362,12 +7362,12 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live (301)</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>DONE — merged into its region hub. The hub already covers this ground, so the old URL 301s to /self-storage/melbourne/ rather than running a second page against it.</t>
         </is>
       </c>
     </row>
@@ -7410,12 +7410,12 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live (301)</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/melbourne/mornington/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Mornington, Melbourne, Victoria, 3931, Australia — 61 km by road from the Melbourne depot at Laverton North.</t>
         </is>
       </c>
     </row>
@@ -7458,12 +7458,12 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live (301)</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/sydney/penrith/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Penrith, Sydney, New South Wales, 2750, Australia — 25 km by road from the Sydney depot at Blacktown.</t>
         </is>
       </c>
     </row>
@@ -7506,12 +7506,12 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live (301)</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/gold-coast/burleigh/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Burleigh Heads, Gold Coast, Queensland, Australia — 56 km by road from the Brisbane depot at Gilberton.</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live (301)</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/melbourne/port-melbourne/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Port Melbourne, Melbourne, Victoria, 3207, Australia — 13 km by road from the Melbourne depot at Laverton North.</t>
         </is>
       </c>
     </row>
@@ -7607,7 +7607,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>BLOCKED, needs one decision: this name is a real suburb in more than one of our cities, so geocoding cannot pick the hub for us. Candidates, each in depot range: Brisbane (37 km, Queensland); Sydney (137 km, New South Wales); Melbourne (71 km, Victoria). Say which one and the page is a few minutes to build.</t>
         </is>
       </c>
     </row>
@@ -7650,12 +7650,12 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live (301)</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/melbourne/south-melbourne/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: South Melbourne, Melbourne, Victoria, 3205, Australia — 18 km by road from the Melbourne depot at Laverton North.</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live (301)</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/melbourne/tullamarine/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Tullamarine, Melbourne, Victoria, 3043, Australia — 19 km by road from the Melbourne depot at Laverton North.</t>
         </is>
       </c>
     </row>
@@ -7746,12 +7746,12 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live (301)</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/melbourne/moorabbin/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Moorabbin, Melbourne, Victoria, 3189, Australia — 33 km by road from the Melbourne depot at Laverton North.</t>
         </is>
       </c>
     </row>
@@ -7794,12 +7794,12 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live (301)</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/brisbane/yatala/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Yatala, Logan City, Queensland, 4207, Australia — 8 km by road from the Brisbane depot at Gilberton.</t>
         </is>
       </c>
     </row>
@@ -7842,12 +7842,12 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live (301)</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/brisbane/capalaba/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Capalaba, Logan City, Brisbane, Redland City, Queensland, Australia — 32 km by road from the Brisbane depot at Gilberton.</t>
         </is>
       </c>
     </row>
@@ -7890,12 +7890,12 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live (301)</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/sydney/north-sydney/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: North Sydney, New South Wales, 2060, Australia — 37 km by road from the Sydney depot at Blacktown.</t>
         </is>
       </c>
     </row>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live (301)</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>DONE — dropped as a service page. Fremantle is in WA and the nearest depot is Adelaide, well past the 200 km standard-delivery range, so a page promising service there would not be true. The old URL 301s to /locations/regional-australia/, which is where a WA enquiry should land.</t>
         </is>
       </c>
     </row>
@@ -7986,12 +7986,12 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live (301)</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/sydney/brookvale/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Brookvale, Northern Beaches, Sydney, New South Wales, Australia — 43 km by road from the Sydney depot at Blacktown.</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live (301)</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/sydney/marrickville/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Marrickville, Inner West, Sydney, New South Wales, 2204, Australia — 36 km by road from the Sydney depot at Blacktown.</t>
         </is>
       </c>
     </row>
@@ -8082,12 +8082,12 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live (301)</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>DONE — merged, not rebuilt. "Eastern Suburbs" is a region, not a suburb, so there is nothing to geocode and no single page it maps to. The old URL 301s to /self-storage/sydney/, which lists every Sydney suburb page beneath it, Bondi Junction among them.</t>
         </is>
       </c>
     </row>
@@ -8135,7 +8135,7 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>BLOCKED, needs one decision: this name is a real suburb in more than one of our cities, so geocoding cannot pick the hub for us. Candidates, each in depot range: Sydney (42 km, New South Wales); Melbourne (15 km, Victoria); Adelaide (30 km, South Australia). Say which one and the page is a few minutes to build.</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live (301)</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/wollongong/unanderra/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Unanderra, Wollongong, New South Wales, Australia — 97 km by road from the Sydney depot at Blacktown.</t>
         </is>
       </c>
     </row>
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live (301)</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/melbourne/north-melbourne/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: North Melbourne, Melbourne, Victoria, 3051, Australia — 16 km by road from the Melbourne depot at Laverton North.</t>
         </is>
       </c>
     </row>
@@ -8274,12 +8274,12 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live (301)</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/brisbane/chermside/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Chermside, Brisbane, Queensland, 4032, Australia — 58 km by road from the Brisbane depot at Gilberton.</t>
         </is>
       </c>
     </row>
@@ -8322,12 +8322,12 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live (301)</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/sydney/gladesville/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Gladesville, Sydney, New South Wales, 2111, Australia — 27 km by road from the Sydney depot at Blacktown.</t>
         </is>
       </c>
     </row>
@@ -8370,12 +8370,12 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live (301)</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/melbourne/altona/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Altona, Melbourne, Victoria, 3018, Australia — 5 km by road from the Melbourne depot at Laverton North.</t>
         </is>
       </c>
     </row>
@@ -8418,12 +8418,12 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live (301)</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/gold-coast/ormeau/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Ormeau, Queensland, Australia — 8 km by road from the Brisbane depot at Gilberton.</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live (301)</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/brisbane/aspley/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Aspley, Brisbane, Queensland, Australia — 62 km by road from the Brisbane depot at Gilberton.</t>
         </is>
       </c>
     </row>
@@ -8514,12 +8514,12 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live (301)</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/brisbane/brendale/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Brendale, Brisbane, Queensland, Australia — 70 km by road from the Brisbane depot at Gilberton.</t>
         </is>
       </c>
     </row>
@@ -8567,7 +8567,7 @@
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>BLOCKED, needs one decision: this name is a real suburb in more than one of our cities, so geocoding cannot pick the hub for us. Candidates, each in depot range: Melbourne (25 km, Victoria); Adelaide (38 km, South Australia). Say which one and the page is a few minutes to build.</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live (301)</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/sydney/rozelle/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Rozelle, Inner West, Sydney, New South Wales, 2039, Australia — 34 km by road from the Sydney depot at Blacktown.</t>
         </is>
       </c>
     </row>
@@ -8658,12 +8658,12 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live (301)</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/sydney/balmain/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Balmain, Inner West, Sydney, New South Wales, 2041, Australia — 34 km by road from the Sydney depot at Blacktown.</t>
         </is>
       </c>
     </row>

--- a/Portabox-SEO-Build-Sheet.xlsx
+++ b/Portabox-SEO-Build-Sheet.xlsx
@@ -7362,12 +7362,12 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>Live (301)</t>
+          <t>Live (308 redirect)</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>DONE — merged into its region hub. The hub already covers this ground, so the old URL 301s to /self-storage/melbourne/ rather than running a second page against it.</t>
+          <t>DONE — merged into its region hub. The hub already covers this ground, so the old URL permanently redirects to /self-storage/melbourne/ rather than running a second page against it.</t>
         </is>
       </c>
     </row>
@@ -7410,12 +7410,12 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>Live (301)</t>
+          <t>Live (308 redirect)</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/melbourne/mornington/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Mornington, Melbourne, Victoria, 3931, Australia — 61 km by road from the Melbourne depot at Laverton North.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL permanently redirects to /self-storage/melbourne/mornington/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Mornington, Melbourne, Victoria, 3931, Australia — 61 km by road from the Melbourne depot at Laverton North.</t>
         </is>
       </c>
     </row>
@@ -7458,12 +7458,12 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>Live (301)</t>
+          <t>Live (308 redirect)</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/sydney/penrith/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Penrith, Sydney, New South Wales, 2750, Australia — 25 km by road from the Sydney depot at Blacktown.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL permanently redirects to /self-storage/sydney/penrith/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Penrith, Sydney, New South Wales, 2750, Australia — 25 km by road from the Sydney depot at Blacktown.</t>
         </is>
       </c>
     </row>
@@ -7506,12 +7506,12 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>Live (301)</t>
+          <t>Live (308 redirect)</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/gold-coast/burleigh/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Burleigh Heads, Gold Coast, Queensland, Australia — 56 km by road from the Brisbane depot at Gilberton.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL permanently redirects to /self-storage/gold-coast/burleigh/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Burleigh Heads, Gold Coast, Queensland, Australia — 56 km by road from the Brisbane depot at Gilberton.</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>Live (301)</t>
+          <t>Live (308 redirect)</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/melbourne/port-melbourne/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Port Melbourne, Melbourne, Victoria, 3207, Australia — 13 km by road from the Melbourne depot at Laverton North.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL permanently redirects to /self-storage/melbourne/port-melbourne/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Port Melbourne, Melbourne, Victoria, 3207, Australia — 13 km by road from the Melbourne depot at Laverton North.</t>
         </is>
       </c>
     </row>
@@ -7650,12 +7650,12 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>Live (301)</t>
+          <t>Live (308 redirect)</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/melbourne/south-melbourne/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: South Melbourne, Melbourne, Victoria, 3205, Australia — 18 km by road from the Melbourne depot at Laverton North.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL permanently redirects to /self-storage/melbourne/south-melbourne/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: South Melbourne, Melbourne, Victoria, 3205, Australia — 18 km by road from the Melbourne depot at Laverton North.</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>Live (301)</t>
+          <t>Live (308 redirect)</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/melbourne/tullamarine/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Tullamarine, Melbourne, Victoria, 3043, Australia — 19 km by road from the Melbourne depot at Laverton North.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL permanently redirects to /self-storage/melbourne/tullamarine/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Tullamarine, Melbourne, Victoria, 3043, Australia — 19 km by road from the Melbourne depot at Laverton North.</t>
         </is>
       </c>
     </row>
@@ -7746,12 +7746,12 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>Live (301)</t>
+          <t>Live (308 redirect)</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/melbourne/moorabbin/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Moorabbin, Melbourne, Victoria, 3189, Australia — 33 km by road from the Melbourne depot at Laverton North.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL permanently redirects to /self-storage/melbourne/moorabbin/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Moorabbin, Melbourne, Victoria, 3189, Australia — 33 km by road from the Melbourne depot at Laverton North.</t>
         </is>
       </c>
     </row>
@@ -7794,12 +7794,12 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>Live (301)</t>
+          <t>Live (308 redirect)</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/brisbane/yatala/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Yatala, Logan City, Queensland, 4207, Australia — 8 km by road from the Brisbane depot at Gilberton.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL permanently redirects to /self-storage/brisbane/yatala/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Yatala, Logan City, Queensland, 4207, Australia — 8 km by road from the Brisbane depot at Gilberton.</t>
         </is>
       </c>
     </row>
@@ -7842,12 +7842,12 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>Live (301)</t>
+          <t>Live (308 redirect)</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/brisbane/capalaba/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Capalaba, Logan City, Brisbane, Redland City, Queensland, Australia — 32 km by road from the Brisbane depot at Gilberton.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL permanently redirects to /self-storage/brisbane/capalaba/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Capalaba, Logan City, Brisbane, Redland City, Queensland, Australia — 32 km by road from the Brisbane depot at Gilberton.</t>
         </is>
       </c>
     </row>
@@ -7890,12 +7890,12 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>Live (301)</t>
+          <t>Live (308 redirect)</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/sydney/north-sydney/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: North Sydney, New South Wales, 2060, Australia — 37 km by road from the Sydney depot at Blacktown.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL permanently redirects to /self-storage/sydney/north-sydney/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: North Sydney, New South Wales, 2060, Australia — 37 km by road from the Sydney depot at Blacktown.</t>
         </is>
       </c>
     </row>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>Live (301)</t>
+          <t>Live (308 redirect)</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>DONE — dropped as a service page. Fremantle is in WA and the nearest depot is Adelaide, well past the 200 km standard-delivery range, so a page promising service there would not be true. The old URL 301s to /locations/regional-australia/, which is where a WA enquiry should land.</t>
+          <t>DONE — dropped as a service page. Fremantle is in WA and the nearest depot is Adelaide, well past the 200 km standard-delivery range, so a page promising service there would not be true. The old URL permanently redirects to /locations/regional-australia/, which is where a WA enquiry should land.</t>
         </is>
       </c>
     </row>
@@ -7986,12 +7986,12 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>Live (301)</t>
+          <t>Live (308 redirect)</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/sydney/brookvale/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Brookvale, Northern Beaches, Sydney, New South Wales, Australia — 43 km by road from the Sydney depot at Blacktown.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL permanently redirects to /self-storage/sydney/brookvale/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Brookvale, Northern Beaches, Sydney, New South Wales, Australia — 43 km by road from the Sydney depot at Blacktown.</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>Live (301)</t>
+          <t>Live (308 redirect)</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/sydney/marrickville/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Marrickville, Inner West, Sydney, New South Wales, 2204, Australia — 36 km by road from the Sydney depot at Blacktown.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL permanently redirects to /self-storage/sydney/marrickville/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Marrickville, Inner West, Sydney, New South Wales, 2204, Australia — 36 km by road from the Sydney depot at Blacktown.</t>
         </is>
       </c>
     </row>
@@ -8082,12 +8082,12 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>Live (301)</t>
+          <t>Live (308 redirect)</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>DONE — merged, not rebuilt. "Eastern Suburbs" is a region, not a suburb, so there is nothing to geocode and no single page it maps to. The old URL 301s to /self-storage/sydney/, which lists every Sydney suburb page beneath it, Bondi Junction among them.</t>
+          <t>DONE — merged, not rebuilt. "Eastern Suburbs" is a region, not a suburb, so there is nothing to geocode and no single page it maps to. The old URL permanently redirects to /self-storage/sydney/, which lists every Sydney suburb page beneath it, Bondi Junction among them.</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>Live (301)</t>
+          <t>Live (308 redirect)</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/wollongong/unanderra/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Unanderra, Wollongong, New South Wales, Australia — 97 km by road from the Sydney depot at Blacktown.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL permanently redirects to /self-storage/wollongong/unanderra/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Unanderra, Wollongong, New South Wales, Australia — 97 km by road from the Sydney depot at Blacktown.</t>
         </is>
       </c>
     </row>
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>Live (301)</t>
+          <t>Live (308 redirect)</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/melbourne/north-melbourne/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: North Melbourne, Melbourne, Victoria, 3051, Australia — 16 km by road from the Melbourne depot at Laverton North.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL permanently redirects to /self-storage/melbourne/north-melbourne/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: North Melbourne, Melbourne, Victoria, 3051, Australia — 16 km by road from the Melbourne depot at Laverton North.</t>
         </is>
       </c>
     </row>
@@ -8274,12 +8274,12 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>Live (301)</t>
+          <t>Live (308 redirect)</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/brisbane/chermside/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Chermside, Brisbane, Queensland, 4032, Australia — 58 km by road from the Brisbane depot at Gilberton.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL permanently redirects to /self-storage/brisbane/chermside/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Chermside, Brisbane, Queensland, 4032, Australia — 58 km by road from the Brisbane depot at Gilberton.</t>
         </is>
       </c>
     </row>
@@ -8322,12 +8322,12 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>Live (301)</t>
+          <t>Live (308 redirect)</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/sydney/gladesville/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Gladesville, Sydney, New South Wales, 2111, Australia — 27 km by road from the Sydney depot at Blacktown.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL permanently redirects to /self-storage/sydney/gladesville/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Gladesville, Sydney, New South Wales, 2111, Australia — 27 km by road from the Sydney depot at Blacktown.</t>
         </is>
       </c>
     </row>
@@ -8370,12 +8370,12 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>Live (301)</t>
+          <t>Live (308 redirect)</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/melbourne/altona/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Altona, Melbourne, Victoria, 3018, Australia — 5 km by road from the Melbourne depot at Laverton North.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL permanently redirects to /self-storage/melbourne/altona/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Altona, Melbourne, Victoria, 3018, Australia — 5 km by road from the Melbourne depot at Laverton North.</t>
         </is>
       </c>
     </row>
@@ -8418,12 +8418,12 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>Live (301)</t>
+          <t>Live (308 redirect)</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/gold-coast/ormeau/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Ormeau, Queensland, Australia — 8 km by road from the Brisbane depot at Gilberton.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL permanently redirects to /self-storage/gold-coast/ormeau/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Ormeau, Queensland, Australia — 8 km by road from the Brisbane depot at Gilberton.</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>Live (301)</t>
+          <t>Live (308 redirect)</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/brisbane/aspley/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Aspley, Brisbane, Queensland, Australia — 62 km by road from the Brisbane depot at Gilberton.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL permanently redirects to /self-storage/brisbane/aspley/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Aspley, Brisbane, Queensland, Australia — 62 km by road from the Brisbane depot at Gilberton.</t>
         </is>
       </c>
     </row>
@@ -8514,12 +8514,12 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>Live (301)</t>
+          <t>Live (308 redirect)</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/brisbane/brendale/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Brendale, Brisbane, Queensland, Australia — 70 km by road from the Brisbane depot at Gilberton.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL permanently redirects to /self-storage/brisbane/brendale/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Brendale, Brisbane, Queensland, Australia — 70 km by road from the Brisbane depot at Gilberton.</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>Live (301)</t>
+          <t>Live (308 redirect)</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/sydney/rozelle/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Rozelle, Inner West, Sydney, New South Wales, 2039, Australia — 34 km by road from the Sydney depot at Blacktown.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL permanently redirects to /self-storage/sydney/rozelle/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Rozelle, Inner West, Sydney, New South Wales, 2039, Australia — 34 km by road from the Sydney depot at Blacktown.</t>
         </is>
       </c>
     </row>
@@ -8658,12 +8658,12 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>Live (301)</t>
+          <t>Live (308 redirect)</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/sydney/balmain/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Balmain, Inner West, Sydney, New South Wales, 2041, Australia — 34 km by road from the Sydney depot at Blacktown.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL permanently redirects to /self-storage/sydney/balmain/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Balmain, Inner West, Sydney, New South Wales, 2041, Australia — 34 km by road from the Sydney depot at Blacktown.</t>
         </is>
       </c>
     </row>
